--- a/Brookline_Enrollment_Explained.xlsx
+++ b/Brookline_Enrollment_Explained.xlsx
@@ -4927,7 +4927,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Assumption: the input in B3</t>
+          <t>Assumption: the input in B3 (counted: 423, Town Clerk, Brookline 2025 Annual Town Report, p.30)</t>
         </is>
       </c>
       <c r="D71" s="23" t="n">

--- a/Brookline_Enrollment_Explained.xlsx
+++ b/Brookline_Enrollment_Explained.xlsx
@@ -240,12 +240,12 @@
     </comment>
     <comment ref="G27" authorId="0" shapeId="0">
       <text>
-        <t>September 2026: K-8 derived from the Superintendent's class-size table (average x sections); 9-12 and BEEP as reported. Approximate to within a student or two per grade.</t>
+        <t>October 1, 2026 (SIMS submission to DESE), as reported by the School Department; the 11 ungraded high school students are in the total but not in a grade.</t>
       </text>
     </comment>
     <comment ref="I27" authorId="0" shapeId="0">
       <text>
-        <t>School Department, September 2026 count</t>
+        <t>School Department, October 1, 2026 count</t>
       </text>
     </comment>
   </commentList>
@@ -260,7 +260,7 @@
   <commentList>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
-        <t>September 2026: K-8 derived from the Superintendent's class-size table (average x sections); 9-12 and BEEP as reported. Approximate to within a student or two per grade.</t>
+        <t>October 1, 2026 (SIMS submission to DESE), as reported by the School Department; the 11 ungraded high school students are in the total but not in a grade.</t>
       </text>
     </comment>
   </commentList>
@@ -300,7 +300,7 @@
   <commentList>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>September 2026: K-8 derived from the Superintendent's class-size table (average x sections); 9-12 and BEEP as reported. Approximate to within a student or two per grade.</t>
+        <t>October 1, 2026 (SIMS submission to DESE), as reported by the School Department; the 11 ungraded high school students are in the total but not in a grade.</t>
       </text>
     </comment>
   </commentList>
@@ -2257,14 +2257,14 @@
         <v/>
       </c>
       <c r="G27" s="12" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H27" s="13">
         <f>G27/E27</f>
         <v/>
       </c>
       <c r="I27" s="12" t="n">
-        <v>6889</v>
+        <v>6833</v>
       </c>
       <c r="J27" s="13">
         <f>I27/F27</f>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="12" t="n">
-        <v>6889</v>
+        <v>6833</v>
       </c>
       <c r="Q27" s="13">
         <f>P27/F27</f>
@@ -2363,10 +2363,10 @@
         <v/>
       </c>
       <c r="O28" s="12" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>6716</v>
+        <v>6662</v>
       </c>
       <c r="Q28" s="13">
         <f>P28/F28</f>
@@ -2444,10 +2444,10 @@
         <v/>
       </c>
       <c r="O29" s="12" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>6554</v>
+        <v>6501</v>
       </c>
       <c r="Q29" s="13">
         <f>P29/F29</f>
@@ -2525,10 +2525,10 @@
         <v/>
       </c>
       <c r="O30" s="12" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>6455</v>
+        <v>6402</v>
       </c>
       <c r="Q30" s="13">
         <f>P30/F30</f>
@@ -2606,10 +2606,10 @@
         <v/>
       </c>
       <c r="O31" s="12" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>6313</v>
+        <v>6262</v>
       </c>
       <c r="Q31" s="13">
         <f>P31/F31</f>
@@ -2687,10 +2687,10 @@
         <v/>
       </c>
       <c r="O32" s="12" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="P32" s="12" t="n">
-        <v>6222</v>
+        <v>6171</v>
       </c>
       <c r="Q32" s="13">
         <f>P32/F32</f>
@@ -2768,10 +2768,10 @@
         <v/>
       </c>
       <c r="O33" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>6104</v>
+        <v>6054</v>
       </c>
       <c r="Q33" s="13">
         <f>P33/F33</f>
@@ -2849,10 +2849,10 @@
         <v/>
       </c>
       <c r="O34" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P34" s="12" t="n">
-        <v>5975</v>
+        <v>5926</v>
       </c>
       <c r="Q34" s="13">
         <f>P34/F34</f>
@@ -2921,10 +2921,10 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
       <c r="O35" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>5854</v>
+        <v>5806</v>
       </c>
       <c r="Q35" s="13">
         <f>P35/F35</f>
@@ -2983,10 +2983,10 @@
       <c r="M36" s="11" t="n"/>
       <c r="N36" s="11" t="n"/>
       <c r="O36" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P36" s="12" t="n">
-        <v>5726</v>
+        <v>5680</v>
       </c>
       <c r="Q36" s="13">
         <f>P36/F36</f>
@@ -3045,10 +3045,10 @@
       <c r="M37" s="11" t="n"/>
       <c r="N37" s="11" t="n"/>
       <c r="O37" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>5630</v>
+        <v>5584</v>
       </c>
       <c r="Q37" s="13">
         <f>P37/F37</f>
@@ -3107,10 +3107,10 @@
       <c r="M38" s="11" t="n"/>
       <c r="N38" s="11" t="n"/>
       <c r="O38" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P38" s="12" t="n">
-        <v>5514</v>
+        <v>5469</v>
       </c>
       <c r="Q38" s="13">
         <f>P38/F38</f>
@@ -3169,10 +3169,10 @@
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>5480</v>
+        <v>5435</v>
       </c>
       <c r="Q39" s="13">
         <f>P39/F39</f>
@@ -3231,10 +3231,10 @@
       <c r="M40" s="11" t="n"/>
       <c r="N40" s="11" t="n"/>
       <c r="O40" s="12" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P40" s="12" t="n">
-        <v>5444</v>
+        <v>5400</v>
       </c>
       <c r="Q40" s="13">
         <f>P40/F40</f>
@@ -3331,14 +3331,14 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>So 415 becomes 415 x 1.029 = 427 in grade 1, then 427 x 1.023 = 437 in grade 2, and so on. The 'Change' columns show each year's ratio. The base case follows the same steps, from NESDEC's numbers scaled up 1.7% to match the September 2026 count (2021 births were already counted, so this class needs no births adjustment).</t>
+          <t>So 415 becomes 415 x 1.029 = 427 in grade 1, then 427 x 1.023 = 437 in grade 2, and so on. The 'Change' columns show each year's ratio. The base case follows the same steps, from NESDEC's numbers scaled up 1.7% to match the October 1, 2026 count (2021 births were already counted, so this class needs no births adjustment).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>The School Department's forecast starts the same class at 507 and keeps it growing: its ratios assume more families moving in at every age. The actual kindergarten in September 2026 was about 411.</t>
+          <t>The School Department's forecast starts the same class at 507 and keeps it growing: its ratios assume more families moving in at every age. The actual kindergarten on October 1, 2026 was 410.</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
         <v>415</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>507</v>
@@ -3429,7 +3429,7 @@
         <v/>
       </c>
       <c r="K10" s="15" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="F11" s="15" t="n">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G11" s="17">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(F10)),F11/F10,"")</f>
@@ -3498,7 +3498,7 @@
         <v/>
       </c>
       <c r="F12" s="15" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G12" s="17">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(F11)),F12/F11,"")</f>
@@ -3540,7 +3540,7 @@
         <v/>
       </c>
       <c r="F13" s="15" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G13" s="17">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(F12)),F13/F12,"")</f>
@@ -3582,7 +3582,7 @@
         <v/>
       </c>
       <c r="F14" s="15" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G14" s="17">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER(F13)),F14/F13,"")</f>
@@ -3624,7 +3624,7 @@
         <v/>
       </c>
       <c r="F15" s="15" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G15" s="17">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(F14)),F15/F14,"")</f>
@@ -3666,7 +3666,7 @@
         <v/>
       </c>
       <c r="F16" s="15" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G16" s="17">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(F15)),F16/F15,"")</f>
@@ -3708,7 +3708,7 @@
         <v/>
       </c>
       <c r="F17" s="15" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G17" s="17">
         <f>IF(AND(ISNUMBER(F17),ISNUMBER(F16)),F17/F16,"")</f>
@@ -3747,7 +3747,7 @@
         <v/>
       </c>
       <c r="F18" s="15" t="n">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G18" s="17">
         <f>IF(AND(ISNUMBER(F18),ISNUMBER(F17)),F18/F17,"")</f>
@@ -3783,7 +3783,7 @@
         <v/>
       </c>
       <c r="F19" s="15" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G19" s="17">
         <f>IF(AND(ISNUMBER(F19),ISNUMBER(F18)),F19/F18,"")</f>
@@ -3819,7 +3819,7 @@
         <v/>
       </c>
       <c r="F20" s="15" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G20" s="17">
         <f>IF(AND(ISNUMBER(F20),ISNUMBER(F19)),F20/F19,"")</f>
@@ -3855,7 +3855,7 @@
         <v/>
       </c>
       <c r="F21" s="15" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G21" s="17">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER(F20)),F21/F20,"")</f>
@@ -3891,7 +3891,7 @@
         <v/>
       </c>
       <c r="F22" s="15" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G22" s="17">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER(F21)),F22/F21,"")</f>
@@ -3909,7 +3909,7 @@
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Kindergarten row: NESDEC's 415 = 491 births x 0.845. Your scenario's kindergarten starts from the September 2026 count (about 411) and follows the ratios on Inputs. Past FY2034 only the base case and Your scenario continue; the base case extends NESDEC's table with its average ratios.</t>
+          <t>Kindergarten row: NESDEC's 415 = 491 births x 0.845. Your scenario's kindergarten starts from the October 1, 2026 count (410) and follows the ratios on Inputs. Past FY2034 only the base case and Your scenario continue; the base case extends NESDEC's table with its average ratios.</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Your scenario: a live cohort model from the September 2026 (FY2027) actual grades</t>
+          <t>Your scenario: a live cohort model from the October 1, 2026 (FY2027) actual grades</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C6" s="25">
         <f>Inputs!$B$5</f>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C7" s="25">
         <f>INDEX(Inputs!$B$26:$B$80,MATCH(C$5,Inputs!$A$26:$A$80,0))*Inputs!$B$4</f>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C8" s="25">
         <f>B7*Inputs!$B$9</f>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C9" s="25">
         <f>B8*Inputs!$B$10</f>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C10" s="25">
         <f>B9*Inputs!$B$11</f>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C11" s="25">
         <f>B10*Inputs!$B$12</f>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C12" s="25">
         <f>B11*Inputs!$B$13</f>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C13" s="25">
         <f>B12*Inputs!$B$14</f>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C14" s="25">
         <f>B13*Inputs!$B$15</f>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C15" s="25">
         <f>B14*Inputs!$B$16</f>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C16" s="25">
         <f>B15*Inputs!$B$17</f>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C17" s="25">
         <f>B16*Inputs!$B$18</f>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C18" s="25">
         <f>B17*Inputs!$B$19</f>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C19" s="25">
         <f>B18*Inputs!$B$20</f>
@@ -6202,46 +6202,46 @@
         </is>
       </c>
       <c r="B23" s="25" t="n">
-        <v>6889</v>
+        <v>6833</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6716</v>
+        <v>6662</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6554</v>
+        <v>6501</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>6455</v>
+        <v>6402</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>6313</v>
+        <v>6262</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>6222</v>
+        <v>6171</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>6104</v>
+        <v>6054</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>5975</v>
+        <v>5926</v>
       </c>
       <c r="J23" s="25" t="n">
-        <v>5854</v>
+        <v>5806</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>5726</v>
+        <v>5680</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>5630</v>
+        <v>5584</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>5514</v>
+        <v>5469</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>5480</v>
+        <v>5435</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>5444</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="24">
@@ -6309,7 +6309,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Why this differs a little from the base case: the base case runs NESDEC's own grade table (adjusted for actual births), scales it to the September 2026 count and adds the children of the Chestnut Hill homes; this sheet starts from the September 2026 grades and applies the ratios directly. The September 2026 grades sum to 6,875 (the reported 6,889 also counts 11 special-program students and rounding).</t>
+          <t>Why this differs a little from the base case: the base case runs NESDEC's own grade table (adjusted for actual births), scales it to the October 1, 2026 count and adds the children of the Chestnut Hill homes; this sheet starts from the October 1, 2026 grades and applies the ratios directly. The October 1, 2026 grades sum to 6,822 (the reported 6,833 also counts 11 ungraded high school students).</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>FY2014-FY2024 from NESDEC's historical table; FY2025-FY2026 from DESE; FY2027 from the Superintendent's September 2026 class-size table (approximate). Excludes ungraded and special-program students.</t>
+          <t>FY2014-FY2024 from NESDEC's historical table; FY2025-FY2026 from DESE; FY2027 from the School Department's October 1, 2026 count. Excludes ungraded and special-program students.</t>
         </is>
       </c>
     </row>
@@ -7145,46 +7145,46 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P19" s="27">
         <f>SUM(B19:O19)</f>
@@ -7873,14 +7873,14 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>Base case: NESDEC adjusted for actual births, scaled to the September 2026 count</t>
+          <t>Base case: NESDEC adjusted for actual births, scaled to the October 1, 2026 count</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Each class born 2022 or later scaled by actual / NESDEC births (2022: 482/459; 2023: 422/518; 2024: 443/507; 2025 on: the 2022-24 average, 449 a year); extended past FY2034 with NESDEC's average ratios; all x 1.017 so FY2027 matches 6,889. The model also adds about 30 children from the Chestnut Hill homes, not shown by grade.</t>
+          <t>Each class born 2022 or later scaled by actual / NESDEC births (2022: 482/459; 2023: 422/518; 2024: 443/507; 2025 on: the 2022-24 average, 449 a year); extended past FY2034 with NESDEC's average ratios; all x 1.009 so FY2027 matches 6,833. The model also adds about 30 children from the Chestnut Hill homes, not shown by grade.</t>
         </is>
       </c>
     </row>
@@ -7973,46 +7973,46 @@
         </is>
       </c>
       <c r="B39" s="15" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C39" s="15" t="n">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="N39" s="15" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="P39" s="27">
         <f>SUM(B39:O39)</f>
@@ -8026,46 +8026,46 @@
         </is>
       </c>
       <c r="B40" s="15" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C40" s="15" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D40" s="15" t="n">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J40" s="15" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L40" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M40" s="15" t="n">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="N40" s="15" t="n">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="P40" s="27">
         <f>SUM(B40:O40)</f>
@@ -8079,46 +8079,46 @@
         </is>
       </c>
       <c r="B41" s="15" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D41" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>502</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>537</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>537</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>554</v>
+      </c>
+      <c r="I41" s="15" t="n">
         <v>515</v>
       </c>
-      <c r="E41" s="15" t="n">
-        <v>506</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>541</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>541</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>558</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>520</v>
-      </c>
       <c r="J41" s="15" t="n">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="N41" s="15" t="n">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="P41" s="27">
         <f>SUM(B41:O41)</f>
@@ -8132,46 +8132,46 @@
         </is>
       </c>
       <c r="B42" s="15" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E42" s="15" t="n">
+        <v>523</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>502</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>542</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>537</v>
+      </c>
+      <c r="I42" s="15" t="n">
         <v>527</v>
       </c>
-      <c r="F42" s="15" t="n">
-        <v>506</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>546</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>541</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>531</v>
-      </c>
       <c r="J42" s="15" t="n">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="L42" s="15" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="M42" s="15" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="N42" s="15" t="n">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="P42" s="27">
         <f>SUM(B42:O42)</f>
@@ -8185,46 +8185,46 @@
         </is>
       </c>
       <c r="B43" s="15" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="L43" s="15" t="n">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N43" s="15" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P43" s="27">
         <f>SUM(B43:O43)</f>
@@ -8238,46 +8238,46 @@
         </is>
       </c>
       <c r="B44" s="15" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="I44" s="15" t="n">
+        <v>515</v>
+      </c>
+      <c r="J44" s="15" t="n">
+        <v>507</v>
+      </c>
+      <c r="K44" s="15" t="n">
         <v>520</v>
       </c>
-      <c r="J44" s="15" t="n">
-        <v>512</v>
-      </c>
-      <c r="K44" s="15" t="n">
-        <v>525</v>
-      </c>
       <c r="L44" s="15" t="n">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="M44" s="15" t="n">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="N44" s="15" t="n">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="P44" s="27">
         <f>SUM(B44:O44)</f>
@@ -8291,46 +8291,46 @@
         </is>
       </c>
       <c r="B45" s="15" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="P45" s="27">
         <f>SUM(B45:O45)</f>
@@ -8344,46 +8344,46 @@
         </is>
       </c>
       <c r="B46" s="15" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D46" s="15" t="n">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="L46" s="15" t="n">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="M46" s="15" t="n">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="N46" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="P46" s="27">
         <f>SUM(B46:O46)</f>
@@ -8397,46 +8397,46 @@
         </is>
       </c>
       <c r="B47" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="P47" s="27">
         <f>SUM(B47:O47)</f>
@@ -8450,46 +8450,46 @@
         </is>
       </c>
       <c r="B48" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D48" s="15" t="n">
+        <v>395</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="F48" s="15" t="n">
         <v>399</v>
       </c>
-      <c r="E48" s="15" t="n">
-        <v>407</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>403</v>
-      </c>
       <c r="G48" s="15" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="L48" s="15" t="n">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="M48" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N48" s="15" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="P48" s="27">
         <f>SUM(B48:O48)</f>
@@ -8503,46 +8503,46 @@
         </is>
       </c>
       <c r="B49" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C49" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I49" s="15" t="n">
+        <v>418</v>
+      </c>
+      <c r="J49" s="15" t="n">
         <v>421</v>
       </c>
-      <c r="J49" s="15" t="n">
-        <v>424</v>
-      </c>
       <c r="K49" s="15" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="P49" s="27">
         <f>SUM(B49:O49)</f>
@@ -8556,46 +8556,46 @@
         </is>
       </c>
       <c r="B50" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C50" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D50" s="15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E50" s="15" t="n">
+        <v>404</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>404</v>
+      </c>
+      <c r="G50" s="15" t="n">
         <v>407</v>
       </c>
-      <c r="F50" s="15" t="n">
-        <v>408</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>411</v>
-      </c>
       <c r="H50" s="15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="L50" s="15" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="M50" s="15" t="n">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N50" s="15" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="P50" s="27">
         <f>SUM(B50:O50)</f>
@@ -8609,46 +8609,46 @@
         </is>
       </c>
       <c r="B51" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C51" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E51" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>404</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>408</v>
+      </c>
+      <c r="H51" s="15" t="n">
         <v>407</v>
       </c>
-      <c r="F51" s="15" t="n">
-        <v>407</v>
-      </c>
-      <c r="G51" s="15" t="n">
-        <v>412</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>411</v>
-      </c>
       <c r="I51" s="15" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K51" s="15" t="n">
+        <v>413</v>
+      </c>
+      <c r="L51" s="15" t="n">
         <v>417</v>
       </c>
-      <c r="L51" s="15" t="n">
+      <c r="M51" s="15" t="n">
         <v>420</v>
       </c>
-      <c r="M51" s="15" t="n">
-        <v>423</v>
-      </c>
       <c r="N51" s="15" t="n">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="P51" s="27">
         <f>SUM(B51:O51)</f>
@@ -8662,46 +8662,46 @@
         </is>
       </c>
       <c r="B52" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C52" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D52" s="15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H52" s="15" t="n">
+        <v>408</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>387</v>
+      </c>
+      <c r="J52" s="15" t="n">
+        <v>382</v>
+      </c>
+      <c r="K52" s="15" t="n">
+        <v>361</v>
+      </c>
+      <c r="L52" s="15" t="n">
         <v>412</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>391</v>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>385</v>
-      </c>
-      <c r="K52" s="15" t="n">
-        <v>364</v>
-      </c>
-      <c r="L52" s="15" t="n">
-        <v>415</v>
-      </c>
       <c r="M52" s="15" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="N52" s="15" t="n">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="P52" s="27">
         <f>SUM(B52:O52)</f>
@@ -8715,46 +8715,46 @@
         </is>
       </c>
       <c r="B53" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C53" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E53" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>407</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>407</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>410</v>
-      </c>
       <c r="H53" s="15" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N53" s="15" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="P53" s="27">
         <f>SUM(B53:O53)</f>
@@ -8768,46 +8768,46 @@
         </is>
       </c>
       <c r="B54" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C54" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D54" s="15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E54" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="G54" s="15" t="n">
         <v>407</v>
       </c>
-      <c r="F54" s="15" t="n">
+      <c r="H54" s="15" t="n">
         <v>407</v>
       </c>
-      <c r="G54" s="15" t="n">
-        <v>410</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>410</v>
-      </c>
       <c r="I54" s="15" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="L54" s="15" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="N54" s="15" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="P54" s="27">
         <f>SUM(B54:O54)</f>
@@ -8821,46 +8821,46 @@
         </is>
       </c>
       <c r="B55" s="15" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C55" s="15" t="n">
+        <v>382</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>394</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>403</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>407</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>407</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>387</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <v>386</v>
+      </c>
+      <c r="K55" s="15" t="n">
         <v>385</v>
       </c>
-      <c r="D55" s="15" t="n">
-        <v>397</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>407</v>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>407</v>
-      </c>
-      <c r="G55" s="15" t="n">
-        <v>410</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>410</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>390</v>
-      </c>
-      <c r="J55" s="15" t="n">
-        <v>389</v>
-      </c>
-      <c r="K55" s="15" t="n">
-        <v>388</v>
-      </c>
       <c r="L55" s="15" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N55" s="15" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="P55" s="27">
         <f>SUM(B55:O55)</f>
